--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>90.0017391304348</v>
+        <v>90.2493706293706</v>
       </c>
       <c r="C167" t="n">
-        <v>81.2559237994696</v>
+        <v>81.4794919927321</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>90.2493706293706</v>
+        <v>90.2762162162162</v>
       </c>
       <c r="C167" t="n">
-        <v>81.4794919927321</v>
+        <v>81.5037288905982</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>90.2762162162162</v>
+        <v>90.242012987013</v>
       </c>
       <c r="C167" t="n">
-        <v>81.5037288905982</v>
+        <v>81.4728493207956</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>90.242012987013</v>
+        <v>90.3242767295597</v>
       </c>
       <c r="C167" t="n">
-        <v>81.4728493207956</v>
+        <v>81.4348240261572</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>90.3242767295597</v>
+        <v>90.4138095238095</v>
       </c>
       <c r="C167" t="n">
-        <v>81.4348240261572</v>
+        <v>81.5155452631081</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>90.4138095238095</v>
+        <v>92.3539890710383</v>
       </c>
       <c r="C167" t="n">
-        <v>81.5155452631081</v>
+        <v>83.1726787618617</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>92.3539890710383</v>
+        <v>93.0270744680851</v>
       </c>
       <c r="C167" t="n">
-        <v>83.1726787618617</v>
+        <v>83.7788498224838</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C03 Figures.xlsx
+++ b/Data/C03 Figures.xlsx
@@ -2215,10 +2215,10 @@
         <v>2026</v>
       </c>
       <c r="B167" t="n">
-        <v>93.0270744680851</v>
+        <v>93.8149222797927</v>
       </c>
       <c r="C167" t="n">
-        <v>83.7788498224838</v>
+        <v>84.4883742687532</v>
       </c>
     </row>
   </sheetData>
